--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/07_vendors_contracts.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/07_vendors_contracts.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rfb33b7ab60cc4833"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Re590b95bbfa14afb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rafe9255ed3e0406c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R5b0737f68c804359"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rdfbd7894b93145a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R52f43f5b14bb4ce8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R835a3676f2b44807"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Ref25a9115aab4328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rf216a696d9334f4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rcb8a481b656f4e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rcce48625fd9740e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R78edfcabe66a4cd8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -626,7 +626,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R405817cb2b5b4f17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46746ef8e62d44d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -797,7 +797,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N6" s="78" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Oracle (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -844,7 +844,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N7" s="79" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm Genesys (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O7" s="45" t="str">
         <x:v>High</x:v>
@@ -891,7 +891,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Workday (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O8" t="str">
         <x:v>Medium</x:v>
@@ -938,7 +938,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Informatica (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O9" t="str">
         <x:v>High</x:v>
@@ -985,7 +985,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O10" t="str">
         <x:v>Medium</x:v>
@@ -1032,7 +1032,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Tableau (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O11" t="str">
         <x:v>High</x:v>
@@ -1079,7 +1079,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm AWS (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O12" t="str">
         <x:v>Medium</x:v>
@@ -1126,7 +1126,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Microsoft (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O13" t="str">
         <x:v>High</x:v>
@@ -1173,7 +1173,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Tableau (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O14" t="str">
         <x:v>Medium</x:v>
@@ -1220,7 +1220,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Epic (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O15" t="str">
         <x:v>High</x:v>
@@ -1267,7 +1267,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate ServiceNow (record 11) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O16" t="str">
         <x:v>Medium</x:v>
@@ -1314,7 +1314,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Optum Managed Services (record 12) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O17" t="str">
         <x:v>High</x:v>
@@ -1361,7 +1361,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Informatica (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O18" t="str">
         <x:v>Medium</x:v>
@@ -1408,7 +1408,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile ServiceNow (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O19" t="str">
         <x:v>High</x:v>
@@ -1455,7 +1455,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Tableau (record 15) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O20" t="str">
         <x:v>Medium</x:v>
@@ -1502,7 +1502,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Epic (record 16) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O21" t="str">
         <x:v>High</x:v>
@@ -1549,7 +1549,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm Salesforce (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O22" t="str">
         <x:v>Medium</x:v>
@@ -1596,7 +1596,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Databricks (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O23" t="str">
         <x:v>High</x:v>
@@ -1643,7 +1643,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Optum Managed Services (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O24" t="str">
         <x:v>Medium</x:v>
@@ -1690,7 +1690,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Workday (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O25" t="str">
         <x:v>High</x:v>
@@ -1737,7 +1737,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Databricks (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O26" t="str">
         <x:v>Medium</x:v>
@@ -1784,7 +1784,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm Tableau (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O27" t="str">
         <x:v>High</x:v>
@@ -1831,7 +1831,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Microsoft (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O28" t="str">
         <x:v>Medium</x:v>
@@ -1878,7 +1878,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Oracle (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O29" t="str">
         <x:v>High</x:v>
@@ -1925,7 +1925,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Genesys (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O30" t="str">
         <x:v>Medium</x:v>
@@ -1972,7 +1972,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate AWS (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O31" t="str">
         <x:v>High</x:v>
@@ -2019,7 +2019,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm Salesforce (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O32" t="str">
         <x:v>Medium</x:v>
@@ -2066,7 +2066,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Databricks (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O33" t="str">
         <x:v>High</x:v>
@@ -2113,7 +2113,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Tableau (record 29) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O34" t="str">
         <x:v>Medium</x:v>
@@ -2160,7 +2160,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Epic (record 30) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O35" t="str">
         <x:v>High</x:v>
@@ -2207,7 +2207,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Epic (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O36" t="str">
         <x:v>Medium</x:v>
@@ -2254,7 +2254,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm Salesforce (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O37" t="str">
         <x:v>High</x:v>
@@ -2301,7 +2301,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Optum Managed Services (record 33), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O38" t="str">
         <x:v>Medium</x:v>
@@ -2348,7 +2348,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Workday (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O39" t="str">
         <x:v>High</x:v>
@@ -2395,7 +2395,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Oracle (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O40" t="str">
         <x:v>Medium</x:v>
@@ -2442,7 +2442,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Validate Genesys (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for vendors contracts.</x:v>
       </x:c>
       <x:c r="O41" t="str">
         <x:v>High</x:v>
@@ -2489,7 +2489,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N42" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm AWS (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this vendors contracts record is used downstream.</x:v>
       </x:c>
       <x:c r="O42" t="str">
         <x:v>Medium</x:v>
@@ -2536,7 +2536,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N43" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Attach client evidence for Microsoft (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O43" t="str">
         <x:v>High</x:v>
@@ -2583,7 +2583,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N44" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Reconcile Optum Managed Services (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O44" t="str">
         <x:v>Medium</x:v>
@@ -2630,7 +2630,7 @@
         <x:v>Procurement lead / technology vendor owner</x:v>
       </x:c>
       <x:c r="N45" t="str">
-        <x:v>Need actual MSA/SOW, pricing schedule, renewal notice window, SLA credits, and termination rights.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Workday (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O45" t="str">
         <x:v>High</x:v>
@@ -2654,7 +2654,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28633bd327a04e4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f7e15fe5d854bfe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2729,7 +2729,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f97060ed3b4608"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b43ddf86db44816"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2913,7 +2913,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R889d65ff20774957"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f488154e4df4009"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2983,7 +2983,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ae48e4f80124d7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd392ca9b43444cad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3093,7 +3093,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51fc5584554440d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61f947f84439416a"/>
   </x:tableParts>
 </x:worksheet>
 </file>